--- a/6.1 Myrmidon disturbance/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/6.1 Myrmidon disturbance/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5.472335176673282</v>
+        <v>5.793188507731652</v>
       </c>
       <c r="C3" t="n">
-        <v>2.488290001187971</v>
+        <v>2.62475318581197</v>
       </c>
       <c r="D3" t="n">
-        <v>19.47793335711897</v>
+        <v>20.14404523996233</v>
       </c>
       <c r="E3" t="n">
-        <v>27.43855853498022</v>
+        <v>28.56198693350595</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.427461161974862</v>
+        <v>1.527868897348536</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8490743194948964</v>
+        <v>0.919166638092287</v>
       </c>
       <c r="D4" t="n">
-        <v>9.72896266945321</v>
+        <v>10.35322562982177</v>
       </c>
       <c r="E4" t="n">
-        <v>12.00549815092297</v>
+        <v>12.8002611652626</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.197976030175929</v>
+        <v>2.357175768605011</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8456283850529901</v>
+        <v>0.9425802260383144</v>
       </c>
       <c r="D5" t="n">
-        <v>9.477438907625178</v>
+        <v>10.38747660989878</v>
       </c>
       <c r="E5" t="n">
-        <v>12.5210433228541</v>
+        <v>13.68723260454211</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3.385674767819636</v>
+        <v>3.602786660383408</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8586463596113028</v>
+        <v>0.9861460268942986</v>
       </c>
       <c r="D6" t="n">
-        <v>9.452581055753649</v>
+        <v>10.672542926852</v>
       </c>
       <c r="E6" t="n">
-        <v>13.69690218318459</v>
+        <v>15.26147561412971</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.960898776760685</v>
+        <v>5.263099469948096</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8726558993509047</v>
+        <v>1.021866606272595</v>
       </c>
       <c r="D7" t="n">
-        <v>9.26713873189847</v>
+        <v>10.75130385750215</v>
       </c>
       <c r="E7" t="n">
-        <v>15.10069340801006</v>
+        <v>17.03626993372283</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.127321435722123</v>
+        <v>7.523577074281489</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8891492607822512</v>
+        <v>1.062017185062492</v>
       </c>
       <c r="D8" t="n">
-        <v>9.184760282035118</v>
+        <v>10.94029249516554</v>
       </c>
       <c r="E8" t="n">
-        <v>17.20123097853949</v>
+        <v>19.52588675450952</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.898392688252127</v>
+        <v>10.39273684596821</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9064574728081225</v>
+        <v>1.109360847653045</v>
       </c>
       <c r="D9" t="n">
-        <v>9.191946675230206</v>
+        <v>11.2597818094254</v>
       </c>
       <c r="E9" t="n">
-        <v>19.99679683629045</v>
+        <v>22.76187950304665</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>13.35149388839943</v>
+        <v>13.89776150183701</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9247081626300707</v>
+        <v>1.155129908381037</v>
       </c>
       <c r="D10" t="n">
-        <v>9.10902826412952</v>
+        <v>11.42520571603493</v>
       </c>
       <c r="E10" t="n">
-        <v>23.38523031515902</v>
+        <v>26.47809712625298</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17.49853363581655</v>
+        <v>18.01091120915219</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9412604289236719</v>
+        <v>1.187437580172563</v>
       </c>
       <c r="D11" t="n">
-        <v>8.914622583734568</v>
+        <v>11.43042938172347</v>
       </c>
       <c r="E11" t="n">
-        <v>27.35441664847479</v>
+        <v>30.62877817104823</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>22.16345511470091</v>
+        <v>22.55422065657581</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9443332992379645</v>
+        <v>1.20963256494164</v>
       </c>
       <c r="D12" t="n">
-        <v>8.628305683268028</v>
+        <v>11.31942839536162</v>
       </c>
       <c r="E12" t="n">
-        <v>31.7360940972069</v>
+        <v>35.08328161687907</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>27.06703946048767</v>
+        <v>27.29327444724159</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9423894387835559</v>
+        <v>1.228739552582233</v>
       </c>
       <c r="D13" t="n">
-        <v>8.551051956420846</v>
+        <v>11.47042747957091</v>
       </c>
       <c r="E13" t="n">
-        <v>36.56048085569207</v>
+        <v>39.99244147939473</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>31.80023167472535</v>
+        <v>31.7931859250573</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9340544007745004</v>
+        <v>1.229367329145089</v>
       </c>
       <c r="D14" t="n">
-        <v>8.260601898119427</v>
+        <v>11.35418053059706</v>
       </c>
       <c r="E14" t="n">
-        <v>40.99488797361927</v>
+        <v>44.37673378479945</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>36.04771402976396</v>
+        <v>35.86216612712579</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9213211330504193</v>
+        <v>1.216021077820987</v>
       </c>
       <c r="D15" t="n">
-        <v>8.110414134323749</v>
+        <v>11.37635728183659</v>
       </c>
       <c r="E15" t="n">
-        <v>45.07944929713813</v>
+        <v>48.45454448678337</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>39.57820640143704</v>
+        <v>39.29524518777611</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9048375890961151</v>
+        <v>1.193127460955855</v>
       </c>
       <c r="D16" t="n">
-        <v>7.769806585812362</v>
+        <v>11.14861463211991</v>
       </c>
       <c r="E16" t="n">
-        <v>48.25285057634552</v>
+        <v>51.63698728085188</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>24.6290752040086</v>
+        <v>24.82807546365943</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6087522989723197</v>
+        <v>0.8011355790965248</v>
       </c>
       <c r="D17" t="n">
-        <v>6.09720302208707</v>
+        <v>8.960548741339233</v>
       </c>
       <c r="E17" t="n">
-        <v>31.33503052506799</v>
+        <v>34.58975978409519</v>
       </c>
     </row>
   </sheetData>
